--- a/data_folder/bev_electronics_boards/input_data/case.xlsx
+++ b/data_folder/bev_electronics_boards/input_data/case.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="90">
   <si>
     <t>key</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>DEFINITIONAL: nothing but copper is recovered from a shredded board. A trace element ground into mixed shredder residue is not separated by anybody, so all of it is lost on this road.</t>
+  </si>
+  <si>
+    <t>scenario_alias</t>
+  </si>
+  <si>
+    <t>*=BAU</t>
   </si>
 </sst>
 </file>
@@ -647,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -741,6 +747,14 @@
       </c>
       <c r="B12" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
